--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484021_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484021_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5726</v>
+        <v>3.1239</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6374</v>
+        <v>0.7098</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0648</v>
+        <v>2.4142</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9557</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4865</v>
+        <v>0.67</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4693</v>
+        <v>0.1813</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4874</v>
+        <v>0.1879</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7243</v>
+        <v>0.9784</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7631</v>
+        <v>-0.7905</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4683</v>
+        <v>0.6634</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2379</v>
+        <v>-0.3083</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7062</v>
+        <v>0.9718</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3832</v>
+        <v>-1.1917</v>
       </c>
       <c r="T2" t="n">
-        <v>0.618</v>
+        <v>-1.0938</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2348</v>
+        <v>-0.0979</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.7502</v>
+        <v>2.0757</v>
       </c>
       <c r="W2" t="n">
-        <v>0.532</v>
+        <v>2.6076</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.2821</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4367</v>
+        <v>1.7166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4434</v>
+        <v>0.9321</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9934</v>
+        <v>0.7845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8512999999999999</v>
+        <v>2.3524</v>
       </c>
       <c r="H3" t="n">
-        <v>0.67</v>
+        <v>1.9754</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1813</v>
+        <v>0.377</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1879</v>
+        <v>2.4624</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9784</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7905</v>
+        <v>-0.0376</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6634</v>
+        <v>-0.11</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3083</v>
+        <v>-0.5246</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9718</v>
+        <v>0.4146</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.879</v>
+        <v>-0.3698</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3602</v>
+        <v>-0.5384</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5187</v>
+        <v>0.1686</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0757</v>
+        <v>-0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6076</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.532</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0406</v>
+        <v>1.631</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3402</v>
+        <v>2.6397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7004</v>
+        <v>-1.0087</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3524</v>
+        <v>2.9557</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9754</v>
+        <v>1.4865</v>
       </c>
       <c r="I4" t="n">
-        <v>0.377</v>
+        <v>1.4693</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4624</v>
+        <v>2.4874</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>1.7243</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0376</v>
+        <v>0.7631</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.11</v>
+        <v>0.4683</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5246</v>
+        <v>-0.2379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4146</v>
+        <v>0.7062</v>
       </c>
       <c r="P4" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.9919</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0459</v>
+        <v>-0.5583</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1303</v>
+        <v>-0.3796</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0844</v>
+        <v>-0.1787</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.266</v>
+        <v>-2.7502</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-3.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. IDOM</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1855</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1491</v>
+        <v>-1.8431</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3346</v>
+        <v>2.5402</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3807</v>
+        <v>-1.0312</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2176</v>
+        <v>0.8111</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8369</v>
+        <v>-1.8423</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5383</v>
+        <v>-0.6014</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1356</v>
+        <v>1.3964</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-1.9979</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1576</v>
+        <v>-0.4298</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9181</v>
+        <v>-0.5853</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2396</v>
+        <v>0.1555</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7271</v>
+        <v>-0.4818</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2356</v>
+        <v>-0.5157</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4916</v>
+        <v>0.0339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.532</v>
+        <v>1.615</v>
       </c>
       <c r="W5" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. IDOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1643</v>
+        <v>0.6444</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3759</v>
+        <v>0.2817</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5402</v>
+        <v>0.3627</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0312</v>
+        <v>1.3807</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8111</v>
+        <v>2.2176</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8423</v>
+        <v>-0.8369</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6014</v>
+        <v>2.5383</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3964</v>
+        <v>3.1356</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9979</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4298</v>
+        <v>-1.1576</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5853</v>
+        <v>-0.9181</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1555</v>
+        <v>-0.2396</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0146</v>
+        <v>-1.2683</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>-0.8048</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0339</v>
+        <v>-0.4635</v>
       </c>
       <c r="V6" t="n">
-        <v>1.615</v>
+        <v>0.532</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X6" t="n">
-        <v>1.349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4329</v>
+        <v>-1.2127</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0862</v>
+        <v>-2.2261</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6533</v>
+        <v>1.0135</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3857</v>
+        <v>2.6587</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8871</v>
+        <v>1.9253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5014</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1591</v>
+        <v>1.9459</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2394</v>
+        <v>1.9058</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0803</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7734</v>
+        <v>0.7127</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3523</v>
+        <v>0.0195</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4211</v>
+        <v>0.6932</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0392</v>
+        <v>-0.4988</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9352</v>
+        <v>-0.4704</v>
       </c>
       <c r="U7" t="n">
-        <v>0.896</v>
+        <v>-0.0284</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4791</v>
+        <v>-1.7976</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4925</v>
+        <v>-3.0862</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0135</v>
+        <v>1.2886</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6587</v>
+        <v>-0.3857</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9253</v>
+        <v>-0.8871</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.5014</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9459</v>
+        <v>-1.1591</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9058</v>
+        <v>-1.2394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0.0803</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7127</v>
+        <v>0.7734</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0195</v>
+        <v>0.3523</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6932</v>
+        <v>0.4211</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.3725</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7652</v>
+        <v>-0.4039</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7368</v>
+        <v>-0.9352</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0284</v>
+        <v>0.5313</v>
       </c>
       <c r="V8" t="n">
+        <v>-1.2065</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="n">
-        <v>0.266</v>
-      </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4665</v>
+        <v>-3.0179</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6296</v>
+        <v>-4.0968</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1631</v>
+        <v>1.0789</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7808</v>
@@ -1156,13 +1156,13 @@
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6262</v>
+        <v>-1.1776</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.6833</v>
+        <v>-1.1505</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0571</v>
+        <v>-0.0271</v>
       </c>
       <c r="V9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6758</v>
+        <v>-6.8161</v>
       </c>
       <c r="E10" t="n">
         <v>-4.6472</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0287</v>
+        <v>-2.1689</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5596</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7114</v>
+        <v>-0.8516</v>
       </c>
       <c r="T10" t="n">
         <v>-0.6858</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0256</v>
+        <v>-0.1658</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4129</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6546</v>
+        <v>-5.0313</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.9595</v>
+        <v>-11.3361</v>
       </c>
       <c r="F11" t="n">
-        <v>6.305</v>
+        <v>6.305000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>5.441500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.720799999999998</v>
+        <v>2.720799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7209</v>
+        <v>2.720899999999999</v>
       </c>
       <c r="J11" t="n">
         <v>4.7069</v>
@@ -1294,7 +1294,7 @@
         <v>-1.5229</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7344999999999998</v>
+        <v>0.7345</v>
       </c>
       <c r="N11" t="n">
         <v>-3.5091</v>
@@ -1312,13 +1312,13 @@
         <v>13.8868</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.425400000000001</v>
+        <v>-6.801800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.197700000000001</v>
+        <v>-6.574199999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2277000000000001</v>
+        <v>-0.2276</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6789</v>
@@ -1327,7 +1327,7 @@
         <v>5.4101</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.088900000000001</v>
+        <v>-8.088899999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4087</v>
+        <v>6.0132</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2542</v>
+        <v>4.6623</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1546</v>
+        <v>1.351</v>
       </c>
       <c r="G12" t="n">
         <v>3.9401</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2783</v>
+        <v>0.8828</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3797</v>
+        <v>0.0284</v>
       </c>
       <c r="U12" t="n">
-        <v>0.658</v>
+        <v>0.8544</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6173</v>
+        <v>3.8554</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2119</v>
+        <v>2.314</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4054</v>
+        <v>1.5414</v>
       </c>
       <c r="G13" t="n">
         <v>2.7501</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2721</v>
+        <v>0.5101</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1189</v>
+        <v>-0.0169</v>
       </c>
       <c r="U13" t="n">
-        <v>0.391</v>
+        <v>0.5271</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6508</v>
+        <v>1.0978</v>
       </c>
       <c r="E14" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.0937</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.6414</v>
+      </c>
+      <c r="H14" t="n">
         <v>-0.9175</v>
       </c>
-      <c r="F14" t="n">
-        <v>2.5683</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.1806</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.0149</v>
-      </c>
       <c r="I14" t="n">
-        <v>-0.1658</v>
+        <v>0.276</v>
       </c>
       <c r="J14" t="n">
-        <v>0.318</v>
+        <v>-0.4133</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2377</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0803</v>
+        <v>0.1205</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4986</v>
+        <v>-0.2281</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2525</v>
+        <v>-0.3837</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2461</v>
+        <v>0.1555</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8946</v>
+        <v>1.2668</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4148</v>
+        <v>0.3969</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4798</v>
+        <v>0.87</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6745</v>
+        <v>0.8692</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6745</v>
+        <v>2.0044</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1199</v>
+        <v>0.637</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1062</v>
+        <v>-1.8634</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0138</v>
+        <v>2.5003</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6414</v>
+        <v>-1.9904</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9175</v>
+        <v>-2.3182</v>
       </c>
       <c r="I15" t="n">
-        <v>0.276</v>
+        <v>0.3278</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4133</v>
+        <v>-1.2869</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-1.3296</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1205</v>
+        <v>0.0427</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2281</v>
+        <v>-0.7035</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3837</v>
+        <v>-0.9885</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1555</v>
+        <v>0.2851</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2889</v>
+        <v>0.6193</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4989</v>
+        <v>-0.4023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.79</v>
+        <v>1.0216</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8692</v>
+        <v>1.8097</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0044</v>
+        <v>1.8097</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.588</v>
+        <v>0.4715</v>
       </c>
       <c r="E16" t="n">
         <v>0.0699</v>
       </c>
       <c r="F16" t="n">
-        <v>0.518</v>
+        <v>0.4016</v>
       </c>
       <c r="G16" t="n">
         <v>-0.868</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7499</v>
+        <v>0.6334</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2946</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0445</v>
+        <v>0.9281</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2777</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4116</v>
+        <v>0.0785</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3735</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7851</v>
+        <v>1.0074</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9904</v>
+        <v>-2.0567</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3182</v>
+        <v>-1.9504</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3278</v>
+        <v>-0.1063</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2869</v>
+        <v>-1.1597</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3296</v>
+        <v>-0.8914</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0427</v>
+        <v>-0.2684</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7035</v>
+        <v>-0.897</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9885</v>
+        <v>-1.059</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2851</v>
+        <v>0.162</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3939</v>
+        <v>0.5158</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9125</v>
+        <v>-0.1983</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3064</v>
+        <v>0.7141</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8097</v>
+        <v>2.4129</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8097</v>
+        <v>2.4129</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2096</v>
+        <v>0.0327</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9113</v>
+        <v>-0.8092</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7017</v>
+        <v>0.8419</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2521</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3542</v>
+        <v>-0.1119</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3117</v>
+        <v>-0.2097</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0425</v>
+        <v>0.0978</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6765</v>
+        <v>-0.4144</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.235</v>
+        <v>-2.754</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5586</v>
+        <v>2.3396</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0567</v>
+        <v>-0.1806</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9504</v>
+        <v>-0.0149</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1063</v>
+        <v>-0.1658</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1597</v>
+        <v>0.318</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8914</v>
+        <v>0.2377</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2684</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.897</v>
+        <v>-0.4986</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.059</v>
+        <v>-0.2525</v>
       </c>
       <c r="O19" t="n">
-        <v>0.162</v>
+        <v>-0.2461</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2392</v>
+        <v>1.8294</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5044</v>
+        <v>0.5783</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2652</v>
+        <v>1.2511</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4129</v>
+        <v>-0.6745</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4129</v>
+        <v>-0.6745</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1149</v>
+        <v>-1.1608</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9585</v>
+        <v>-2.0606</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8436</v>
+        <v>0.8998</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1645</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5735</v>
+        <v>1.5276</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7483</v>
+        <v>0.6463</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8252</v>
+        <v>0.8813</v>
       </c>
       <c r="V20" t="n">
         <v>0.0713</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4515</v>
+        <v>-2.0051</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8103</v>
+        <v>-2.5042</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3588</v>
+        <v>0.499</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7179</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2692</v>
+        <v>0.1772</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3627</v>
+        <v>-0.0566</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0935</v>
+        <v>0.2338</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6893</v>
+        <v>-2.271</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7411</v>
+        <v>-2.435</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0518</v>
+        <v>0.164</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2601</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1632</v>
+        <v>0.2551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5498</v>
+        <v>-0.2437</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3865</v>
+        <v>0.4988</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.654500000000001</v>
+        <v>6.3348</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.305</v>
+        <v>-6.3049</v>
       </c>
       <c r="F23" t="n">
-        <v>11.9597</v>
+        <v>12.6397</v>
       </c>
       <c r="G23" t="n">
         <v>-5.4415</v>
@@ -2218,7 +2218,7 @@
         <v>-2.721</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.720800000000001</v>
+        <v>-2.7208</v>
       </c>
       <c r="J23" t="n">
         <v>-0.7344999999999999</v>
@@ -2239,7 +2239,7 @@
         <v>1.5228</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9918999999999997</v>
+        <v>0.9919000000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.8867</v>
@@ -2248,19 +2248,19 @@
         <v>14.8788</v>
       </c>
       <c r="S23" t="n">
-        <v>7.425400000000001</v>
+        <v>8.105599999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2276999999999997</v>
+        <v>0.2278</v>
       </c>
       <c r="U23" t="n">
-        <v>7.1976</v>
+        <v>7.878100000000001</v>
       </c>
       <c r="V23" t="n">
         <v>2.6789</v>
       </c>
       <c r="W23" t="n">
-        <v>8.088799999999999</v>
+        <v>8.088800000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-5.41</v>
